--- a/March_Release_SCB_UAT/Cypress/fixtures/StaffTemplate.xlsx
+++ b/March_Release_SCB_UAT/Cypress/fixtures/StaffTemplate.xlsx
@@ -433,19 +433,19 @@
         <v>Others</v>
       </c>
       <c r="B2" t="str">
-        <v>13643</v>
+        <v>36184</v>
       </c>
       <c r="C2" t="str">
-        <v>Susana</v>
+        <v>Ron</v>
       </c>
       <c r="D2" t="str">
-        <v>Hauck</v>
+        <v>Upton</v>
       </c>
       <c r="E2" t="str">
-        <v>susana@yopmail.com</v>
+        <v>ron@yopmail.com</v>
       </c>
       <c r="F2" t="str">
-        <v>2518061700</v>
+        <v>2506332072</v>
       </c>
       <c r="G2" t="str">
         <v>Branch Backend</v>

--- a/March_Release_SCB_UAT/Cypress/fixtures/StaffTemplate.xlsx
+++ b/March_Release_SCB_UAT/Cypress/fixtures/StaffTemplate.xlsx
@@ -433,19 +433,19 @@
         <v>Others</v>
       </c>
       <c r="B2" t="str">
-        <v>36184</v>
+        <v>32109</v>
       </c>
       <c r="C2" t="str">
-        <v>Ron</v>
+        <v>Coleman</v>
       </c>
       <c r="D2" t="str">
-        <v>Upton</v>
+        <v>Jones</v>
       </c>
       <c r="E2" t="str">
-        <v>ron@yopmail.com</v>
+        <v>coleman@yopmail.com</v>
       </c>
       <c r="F2" t="str">
-        <v>2506332072</v>
+        <v>6938842636</v>
       </c>
       <c r="G2" t="str">
         <v>Branch Backend</v>
